--- a/data/trans_dic/P19C09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C09-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos (tasa de respuesta: 99,04%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,27</t>
+          <t>0,54; 3,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,97</t>
+          <t>1,53; 4,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,78</t>
+          <t>1,17; 4,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,35</t>
+          <t>1,11; 5,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,8</t>
+          <t>1,87; 7,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,07</t>
+          <t>1,62; 6,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,33</t>
+          <t>1,14; 3,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,07</t>
+          <t>2,14; 5,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,66</t>
+          <t>1,85; 4,64</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,64</t>
+          <t>0,64; 4,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,19</t>
+          <t>0,82; 4,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,16</t>
+          <t>0,64; 4,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,37</t>
+          <t>0,9; 4,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,68</t>
+          <t>2,14; 7,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,54</t>
+          <t>1,47; 5,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,54</t>
+          <t>1,08; 3,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,82</t>
+          <t>1,79; 4,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,99</t>
+          <t>1,4; 4,0</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,5</t>
+          <t>1,72; 5,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,93</t>
+          <t>0,94; 3,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,53</t>
+          <t>1,46; 4,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 7,0</t>
+          <t>0,84; 7,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,51</t>
+          <t>1,25; 6,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,99</t>
+          <t>1,77; 5,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,87</t>
+          <t>1,4; 3,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,49</t>
+          <t>1,06; 3,49</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,45</t>
+          <t>1,92; 4,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,37</t>
+          <t>0,72; 2,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,16</t>
+          <t>1,88; 4,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,57</t>
+          <t>1,07; 3,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,92</t>
+          <t>1,42; 3,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,08</t>
+          <t>1,46; 4,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,61</t>
+          <t>1,9; 3,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,55</t>
+          <t>1,12; 2,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,56</t>
+          <t>1,92; 3,61</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,51</t>
+          <t>1,89; 6,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,6</t>
+          <t>0,27; 3,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,51</t>
+          <t>1,83; 5,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,56</t>
+          <t>1,89; 5,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,48</t>
+          <t>1,12; 3,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,57</t>
+          <t>1,57; 4,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,4</t>
+          <t>2,45; 5,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,92</t>
+          <t>1,09; 2,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,26</t>
+          <t>2,02; 4,23</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,65</t>
+          <t>0,8; 4,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,97</t>
+          <t>0,43; 4,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 8,05</t>
+          <t>2,34; 8,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,41</t>
+          <t>2,97; 5,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,0</t>
+          <t>1,65; 3,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,11</t>
+          <t>1,72; 4,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,97</t>
+          <t>2,75; 4,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,58</t>
+          <t>1,58; 3,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,32</t>
+          <t>2,18; 4,51</t>
         </is>
       </c>
     </row>
@@ -1338,37 +1338,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,39</t>
+          <t>2,03; 3,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,33</t>
+          <t>1,28; 2,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,58</t>
+          <t>2,25; 3,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,81</t>
+          <t>2,57; 3,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,55</t>
+          <t>2,23; 3,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,36</t>
+          <t>2,1; 3,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,45</t>
+          <t>2,41; 3,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,24</t>
+          <t>2,33; 3,26</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos (tasa de respuesta: 99,04%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2511; 12619</t>
+          <t>2100; 11691</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5858; 18856</t>
+          <t>5804; 18153</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4278; 18517</t>
+          <t>4531; 17855</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2923; 14344</t>
+          <t>2988; 15626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5675; 22031</t>
+          <t>5281; 20420</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5024; 19165</t>
+          <t>5131; 19225</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6656; 21772</t>
+          <t>7460; 23016</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13749; 33565</t>
+          <t>14161; 33715</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13331; 32803</t>
+          <t>13043; 32658</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1937; 13937</t>
+          <t>1923; 12830</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2938; 15586</t>
+          <t>3041; 17000</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2061; 13165</t>
+          <t>2014; 13554</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2983; 14476</t>
+          <t>2978; 14258</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6687; 23853</t>
+          <t>6640; 24386</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5430; 18470</t>
+          <t>4913; 18846</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7152; 22392</t>
+          <t>6840; 22576</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12195; 32860</t>
+          <t>12215; 33174</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8910; 25965</t>
+          <t>9114; 26030</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7122; 23624</t>
+          <t>7400; 22802</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5868; 20633</t>
+          <t>4957; 19434</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5216; 18343</t>
+          <t>5902; 18939</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1001; 9811</t>
+          <t>1180; 9970</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2966; 13095</t>
+          <t>2964; 14941</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2057</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10367; 28420</t>
+          <t>10103; 28459</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10127; 29508</t>
+          <t>10695; 28055</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5869; 19001</t>
+          <t>5747; 19017</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17251; 38672</t>
+          <t>16671; 37496</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6738; 22530</t>
+          <t>6887; 23357</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15863; 36553</t>
+          <t>16536; 37128</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6730; 21309</t>
+          <t>6397; 20348</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8981; 26474</t>
+          <t>9624; 26507</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9547; 27942</t>
+          <t>9977; 27454</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27276; 52897</t>
+          <t>27887; 52699</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18893; 41577</t>
+          <t>18245; 41312</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30368; 55702</t>
+          <t>30033; 56508</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4683; 16092</t>
+          <t>4660; 16126</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1102; 14156</t>
+          <t>1060; 13134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7982; 23442</t>
+          <t>7783; 22236</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9121; 25372</t>
+          <t>8618; 24769</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7406; 22873</t>
+          <t>7392; 23601</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9299; 25494</t>
+          <t>8773; 25111</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17566; 38006</t>
+          <t>17248; 38357</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11327; 30669</t>
+          <t>11483; 30465</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19693; 41886</t>
+          <t>19869; 41556</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1724; 9876</t>
+          <t>1688; 9965</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>906; 8464</t>
+          <t>908; 8574</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5617; 19438</t>
+          <t>5659; 20330</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28596; 51055</t>
+          <t>28005; 52331</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14637; 36118</t>
+          <t>14852; 35783</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14142; 33953</t>
+          <t>14171; 33604</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30640; 57496</t>
+          <t>31841; 56659</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17962; 39981</t>
+          <t>17580; 39890</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23708; 46107</t>
+          <t>23248; 48103</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>51121; 82872</t>
+          <t>49736; 82585</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35745; 65961</t>
+          <t>36186; 64162</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59147; 94975</t>
+          <t>59857; 95442</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68598; 104192</t>
+          <t>70230; 106001</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>67925; 108895</t>
+          <t>68284; 107982</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59436; 95942</t>
+          <t>60078; 97426</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>128453; 178874</t>
+          <t>124866; 175572</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>111992; 161779</t>
+          <t>111884; 161929</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>129678; 178819</t>
+          <t>128410; 179762</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C09-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,03</t>
+          <t>0,53; 2,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,79</t>
+          <t>1,53; 4,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,61</t>
+          <t>1,22; 4,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,82</t>
+          <t>1,14; 5,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,23</t>
+          <t>1,98; 7,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,09</t>
+          <t>1,58; 6,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,52</t>
+          <t>1,18; 3,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,09</t>
+          <t>2,08; 5,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,64</t>
+          <t>1,79; 4,52</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,27</t>
+          <t>0,65; 4,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,57</t>
+          <t>0,78; 4,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,28</t>
+          <t>0,65; 4,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,3</t>
+          <t>1,03; 4,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,86</t>
+          <t>2,26; 7,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,65</t>
+          <t>1,59; 5,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,57</t>
+          <t>1,1; 3,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,86</t>
+          <t>1,79; 5,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,0</t>
+          <t>1,51; 4,13</t>
         </is>
       </c>
     </row>
@@ -898,27 +898,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,31</t>
+          <t>1,54; 5,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,7</t>
+          <t>1,12; 3,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,67</t>
+          <t>1,34; 4,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,12</t>
+          <t>0,72; 6,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,29</t>
+          <t>1,27; 6,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,0</t>
+          <t>1,89; 5,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,68</t>
+          <t>1,43; 3,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,49</t>
+          <t>1,04; 3,6</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,31</t>
+          <t>1,96; 4,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,45</t>
+          <t>0,61; 2,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,22</t>
+          <t>1,88; 4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,41</t>
+          <t>1,12; 3,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,92</t>
+          <t>1,35; 4,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,01</t>
+          <t>1,41; 3,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,6</t>
+          <t>1,83; 3,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,54</t>
+          <t>1,14; 2,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,61</t>
+          <t>1,93; 3,63</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,53</t>
+          <t>1,86; 6,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,34</t>
+          <t>0,5; 3,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,23</t>
+          <t>1,8; 5,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,43</t>
+          <t>2,14; 5,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,59</t>
+          <t>1,13; 3,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,5</t>
+          <t>1,65; 4,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,45</t>
+          <t>2,44; 5,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,9</t>
+          <t>1,01; 2,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,23</t>
+          <t>2,03; 4,25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,7</t>
+          <t>0,81; 4,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,02</t>
+          <t>0,43; 4,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,42</t>
+          <t>2,29; 8,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,54</t>
+          <t>2,81; 5,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,97</t>
+          <t>1,71; 3,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,07</t>
+          <t>1,79; 4,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,9</t>
+          <t>2,71; 5,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,58</t>
+          <t>1,6; 3,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,51</t>
+          <t>2,17; 4,35</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,38</t>
+          <t>2,04; 3,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,26</t>
+          <t>1,21; 2,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,59</t>
+          <t>2,32; 3,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,87</t>
+          <t>2,45; 3,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,52</t>
+          <t>2,24; 3,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,41</t>
+          <t>2,06; 3,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,39</t>
+          <t>2,45; 3,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,74</t>
+          <t>1,89; 2,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,26</t>
+          <t>2,33; 3,29</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2100; 11691</t>
+          <t>2045; 11384</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5804; 18153</t>
+          <t>5817; 18420</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4531; 17855</t>
+          <t>4729; 17684</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2988; 15626</t>
+          <t>3065; 15181</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5281; 20420</t>
+          <t>5589; 21781</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5131; 19225</t>
+          <t>4989; 19358</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7460; 23016</t>
+          <t>7695; 23597</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14161; 33715</t>
+          <t>13788; 33406</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13043; 32658</t>
+          <t>12562; 31764</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1923; 12830</t>
+          <t>1938; 12645</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3041; 17000</t>
+          <t>2915; 15057</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2014; 13554</t>
+          <t>2054; 13122</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2978; 14258</t>
+          <t>3399; 14230</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6640; 24386</t>
+          <t>7023; 24526</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4913; 18846</t>
+          <t>5290; 18316</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6840; 22576</t>
+          <t>6922; 22371</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12215; 33174</t>
+          <t>12189; 35664</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9114; 26030</t>
+          <t>9833; 26865</t>
         </is>
       </c>
     </row>
@@ -1965,27 +1965,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7400; 22802</t>
+          <t>6605; 22559</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4957; 19434</t>
+          <t>5865; 19605</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5902; 18939</t>
+          <t>5441; 19316</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1180; 9970</t>
+          <t>1005; 9638</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2964; 14941</t>
+          <t>3020; 14732</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10103; 28459</t>
+          <t>10747; 28751</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10695; 28055</t>
+          <t>10929; 28497</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5747; 19017</t>
+          <t>5683; 19627</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16671; 37496</t>
+          <t>17035; 37246</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6887; 23357</t>
+          <t>5803; 20827</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16536; 37128</t>
+          <t>16560; 35442</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6397; 20348</t>
+          <t>6693; 21521</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9624; 26507</t>
+          <t>9095; 27061</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9977; 27454</t>
+          <t>9636; 27162</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27887; 52699</t>
+          <t>26848; 50678</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18245; 41312</t>
+          <t>18491; 42346</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30033; 56508</t>
+          <t>30177; 56758</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4660; 16126</t>
+          <t>4605; 17199</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1060; 13134</t>
+          <t>1981; 13943</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7783; 22236</t>
+          <t>7661; 23927</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8618; 24769</t>
+          <t>9779; 26241</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7392; 23601</t>
+          <t>7407; 23183</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8773; 25111</t>
+          <t>9224; 25038</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17248; 38357</t>
+          <t>17141; 39780</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11483; 30465</t>
+          <t>10652; 28662</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19869; 41556</t>
+          <t>19986; 41756</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1688; 9965</t>
+          <t>1709; 10079</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>908; 8574</t>
+          <t>918; 8816</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5659; 20330</t>
+          <t>5542; 19416</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28005; 52331</t>
+          <t>26494; 50324</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14852; 35783</t>
+          <t>15401; 35142</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14171; 33604</t>
+          <t>14737; 34548</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31841; 56659</t>
+          <t>31290; 59149</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17580; 39890</t>
+          <t>17832; 39107</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23248; 48103</t>
+          <t>23195; 46373</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>49736; 82585</t>
+          <t>49741; 81024</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>36186; 64162</t>
+          <t>34383; 63383</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59857; 95442</t>
+          <t>61543; 95440</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70230; 106001</t>
+          <t>67083; 105578</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>68284; 107982</t>
+          <t>68684; 104674</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60078; 97426</t>
+          <t>58689; 95586</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>124866; 175572</t>
+          <t>126750; 176556</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>111884; 161929</t>
+          <t>111545; 158922</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>128410; 179762</t>
+          <t>128650; 181229</t>
         </is>
       </c>
     </row>
